--- a/StructureDefinition-onc-sleep-pattern.xlsx
+++ b/StructureDefinition-onc-sleep-pattern.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-03T01:44:04+00:00</t>
+    <t>2026-01-03T21:32:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-sleep-pattern.xlsx
+++ b/StructureDefinition-onc-sleep-pattern.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-03T21:32:36+00:00</t>
+    <t>2026-01-26T10:54:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-sleep-pattern.xlsx
+++ b/StructureDefinition-onc-sleep-pattern.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T10:54:48+00:00</t>
+    <t>2026-01-26T11:35:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-sleep-pattern.xlsx
+++ b/StructureDefinition-onc-sleep-pattern.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T11:35:16+00:00</t>
+    <t>2026-01-26T23:55:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-sleep-pattern.xlsx
+++ b/StructureDefinition-onc-sleep-pattern.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T23:55:12+00:00</t>
+    <t>2026-01-27T00:24:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-sleep-pattern.xlsx
+++ b/StructureDefinition-onc-sleep-pattern.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://fhir.clinyq.ai/StructureDefinition/onc-sleep-pattern</t>
+    <t>https://opennursingcoreig.com/StructureDefinition/onc-sleep-pattern</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-27T00:24:44+00:00</t>
+    <t>2026-01-27T01:09:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-sleep-pattern.xlsx
+++ b/StructureDefinition-onc-sleep-pattern.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-27T01:09:05+00:00</t>
+    <t>2026-01-27T08:26:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-sleep-pattern.xlsx
+++ b/StructureDefinition-onc-sleep-pattern.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-27T08:26:02+00:00</t>
+    <t>2026-01-27T09:30:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-sleep-pattern.xlsx
+++ b/StructureDefinition-onc-sleep-pattern.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-27T09:30:37+00:00</t>
+    <t>2026-06-29T21:13:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-sleep-pattern.xlsx
+++ b/StructureDefinition-onc-sleep-pattern.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T21:13:26+00:00</t>
+    <t>2026-07-04T08:39:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-sleep-pattern.xlsx
+++ b/StructureDefinition-onc-sleep-pattern.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-04T08:39:09+00:00</t>
+    <t>2026-07-04T09:17:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-sleep-pattern.xlsx
+++ b/StructureDefinition-onc-sleep-pattern.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-04T09:17:49+00:00</t>
+    <t>2026-07-09T21:51:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-sleep-pattern.xlsx
+++ b/StructureDefinition-onc-sleep-pattern.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T21:51:52+00:00</t>
+    <t>2026-07-09T22:02:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-sleep-pattern.xlsx
+++ b/StructureDefinition-onc-sleep-pattern.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T22:02:23+00:00</t>
+    <t>2026-07-09T22:05:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-sleep-pattern.xlsx
+++ b/StructureDefinition-onc-sleep-pattern.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T22:05:12+00:00</t>
+    <t>2026-07-09T22:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-sleep-pattern.xlsx
+++ b/StructureDefinition-onc-sleep-pattern.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T22:28:17+00:00</t>
+    <t>2026-07-10T11:01:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-sleep-pattern.xlsx
+++ b/StructureDefinition-onc-sleep-pattern.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T11:01:35+00:00</t>
+    <t>2026-07-11T09:35:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-sleep-pattern.xlsx
+++ b/StructureDefinition-onc-sleep-pattern.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3347" uniqueCount="541">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3347" uniqueCount="540">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T09:35:24+00:00</t>
+    <t>2026-07-11T09:46:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -617,14 +617,6 @@
   </si>
   <si>
     <t>Used for filtering what observations are retrieved and displayed.</t>
-  </si>
-  <si>
-    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;system value="http://terminology.hl7.org/CodeSystem/observation-category"/&gt;
-    &lt;code value="exam"/&gt;
-  &lt;/coding&gt;
-&lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
     <t>Codes for high level observation categories.</t>
@@ -3827,7 +3819,7 @@
         <v>18</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>193</v>
+        <v>18</v>
       </c>
       <c r="T15" t="s" s="2">
         <v>18</v>
@@ -3845,23 +3837,23 @@
         <v>114</v>
       </c>
       <c r="Y15" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="Z15" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="Z15" t="s" s="2">
+      <c r="AA15" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB15" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AF15" t="s" s="2">
         <v>187</v>
@@ -3888,10 +3880,10 @@
         <v>18</v>
       </c>
       <c r="AN15" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AO15" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="AO15" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>18</v>
@@ -3899,13 +3891,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B16" t="s" s="2">
         <v>187</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>18</v>
@@ -3949,7 +3941,7 @@
         <v>18</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>18</v>
@@ -3967,10 +3959,10 @@
         <v>114</v>
       </c>
       <c r="Y16" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="Z16" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="Z16" t="s" s="2">
-        <v>195</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>18</v>
@@ -4012,10 +4004,10 @@
         <v>18</v>
       </c>
       <c r="AN16" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AO16" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="AO16" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>18</v>
@@ -4023,14 +4015,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -4052,16 +4044,16 @@
         <v>188</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="N17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>18</v>
@@ -4071,29 +4063,29 @@
         <v>18</v>
       </c>
       <c r="S17" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="T17" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U17" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V17" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W17" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X17" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="T17" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="U17" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="V17" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="W17" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="X17" t="s" s="2">
+      <c r="Y17" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="Y17" t="s" s="2">
+      <c r="Z17" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="Z17" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="AA17" t="s" s="2">
         <v>18</v>
       </c>
@@ -4110,7 +4102,7 @@
         <v>18</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>90</v>
@@ -4125,30 +4117,30 @@
         <v>102</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="AL17" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="AL17" t="s" s="2">
+      <c r="AM17" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="AM17" t="s" s="2">
+      <c r="AN17" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AN17" t="s" s="2">
+      <c r="AO17" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="AO17" t="s" s="2">
+      <c r="AP17" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="AP17" t="s" s="2">
-        <v>218</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4171,19 +4163,19 @@
         <v>91</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="N18" t="s" s="2">
+      <c r="O18" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>18</v>
@@ -4232,7 +4224,7 @@
         <v>18</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -4247,19 +4239,19 @@
         <v>102</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AL18" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM18" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="AL18" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM18" t="s" s="2">
+      <c r="AN18" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="AN18" t="s" s="2">
+      <c r="AO18" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>18</v>
@@ -4267,10 +4259,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4293,16 +4285,16 @@
         <v>91</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4352,7 +4344,7 @@
         <v>18</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -4373,13 +4365,13 @@
         <v>18</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>18</v>
@@ -4387,14 +4379,14 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4413,19 +4405,19 @@
         <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>237</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="N20" t="s" s="2">
+      <c r="O20" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>18</v>
@@ -4474,7 +4466,7 @@
         <v>18</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -4489,19 +4481,19 @@
         <v>102</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM20" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="AL20" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM20" t="s" s="2">
+      <c r="AN20" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="AN20" t="s" s="2">
+      <c r="AO20" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>245</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>18</v>
@@ -4509,14 +4501,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4535,19 +4527,19 @@
         <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="N21" t="s" s="2">
+      <c r="O21" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>252</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>18</v>
@@ -4596,7 +4588,7 @@
         <v>18</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4611,19 +4603,19 @@
         <v>102</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM21" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="AL21" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM21" t="s" s="2">
+      <c r="AN21" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="AN21" t="s" s="2">
+      <c r="AO21" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>256</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>18</v>
@@ -4631,10 +4623,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4657,16 +4649,16 @@
         <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4716,7 +4708,7 @@
         <v>18</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4737,13 +4729,13 @@
         <v>18</v>
       </c>
       <c r="AM22" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="AN22" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="AN22" t="s" s="2">
+      <c r="AO22" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>264</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>18</v>
@@ -4751,10 +4743,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4777,17 +4769,17 @@
         <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>18</v>
@@ -4836,7 +4828,7 @@
         <v>18</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4851,19 +4843,19 @@
         <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM23" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="AL23" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM23" t="s" s="2">
+      <c r="AN23" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="AN23" t="s" s="2">
+      <c r="AO23" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>18</v>
@@ -4871,10 +4863,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4897,19 +4889,19 @@
         <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="N24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>279</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>18</v>
@@ -4958,7 +4950,7 @@
         <v>18</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4967,7 +4959,7 @@
         <v>90</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>102</v>
@@ -4976,27 +4968,27 @@
         <v>18</v>
       </c>
       <c r="AL24" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AM24" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="AM24" t="s" s="2">
+      <c r="AN24" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AN24" t="s" s="2">
+      <c r="AO24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP24" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="AO24" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP24" t="s" s="2">
-        <v>284</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5022,16 +5014,16 @@
         <v>188</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="N25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>289</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>18</v>
@@ -5056,14 +5048,14 @@
         <v>18</v>
       </c>
       <c r="X25" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="Y25" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="Y25" t="s" s="2">
+      <c r="Z25" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="Z25" t="s" s="2">
-        <v>292</v>
-      </c>
       <c r="AA25" t="s" s="2">
         <v>18</v>
       </c>
@@ -5080,7 +5072,7 @@
         <v>18</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -5089,7 +5081,7 @@
         <v>90</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>102</v>
@@ -5104,7 +5096,7 @@
         <v>133</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>18</v>
@@ -5115,14 +5107,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -5144,16 +5136,16 @@
         <v>188</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="N26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>18</v>
@@ -5178,14 +5170,14 @@
         <v>18</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Y26" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="Z26" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="Z26" t="s" s="2">
-        <v>302</v>
-      </c>
       <c r="AA26" t="s" s="2">
         <v>18</v>
       </c>
@@ -5202,7 +5194,7 @@
         <v>18</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -5220,27 +5212,27 @@
         <v>18</v>
       </c>
       <c r="AL26" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AM26" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="AM26" t="s" s="2">
+      <c r="AN26" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="AN26" t="s" s="2">
+      <c r="AO26" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP26" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP26" t="s" s="2">
-        <v>306</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5263,19 +5255,19 @@
         <v>18</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="N27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>18</v>
@@ -5324,7 +5316,7 @@
         <v>18</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -5345,10 +5337,10 @@
         <v>18</v>
       </c>
       <c r="AM27" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>18</v>
@@ -5359,10 +5351,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5388,13 +5380,13 @@
         <v>188</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5420,14 +5412,14 @@
         <v>18</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Y28" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="Z28" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="Z28" t="s" s="2">
-        <v>320</v>
-      </c>
       <c r="AA28" t="s" s="2">
         <v>18</v>
       </c>
@@ -5444,7 +5436,7 @@
         <v>18</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -5462,27 +5454,27 @@
         <v>18</v>
       </c>
       <c r="AL28" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AM28" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="AM28" t="s" s="2">
+      <c r="AN28" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="AN28" t="s" s="2">
+      <c r="AO28" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP28" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="AO28" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP28" t="s" s="2">
-        <v>324</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5508,16 +5500,16 @@
         <v>188</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="N29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>329</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>18</v>
@@ -5542,14 +5534,14 @@
         <v>18</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Y29" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="Z29" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="Z29" t="s" s="2">
-        <v>331</v>
-      </c>
       <c r="AA29" t="s" s="2">
         <v>18</v>
       </c>
@@ -5566,7 +5558,7 @@
         <v>18</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5587,10 +5579,10 @@
         <v>18</v>
       </c>
       <c r="AM29" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>18</v>
@@ -5601,10 +5593,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5627,16 +5619,16 @@
         <v>18</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>338</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5686,7 +5678,7 @@
         <v>18</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5704,27 +5696,27 @@
         <v>18</v>
       </c>
       <c r="AL30" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="AM30" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="AM30" t="s" s="2">
+      <c r="AN30" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="AN30" t="s" s="2">
+      <c r="AO30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP30" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP30" t="s" s="2">
-        <v>342</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5747,16 +5739,16 @@
         <v>18</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5806,7 +5798,7 @@
         <v>18</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5824,27 +5816,27 @@
         <v>18</v>
       </c>
       <c r="AL31" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AM31" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="AM31" t="s" s="2">
+      <c r="AN31" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="AN31" t="s" s="2">
+      <c r="AO31" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP31" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="AO31" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP31" t="s" s="2">
-        <v>351</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5867,19 +5859,19 @@
         <v>18</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="N32" t="s" s="2">
+      <c r="O32" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>18</v>
@@ -5928,7 +5920,7 @@
         <v>18</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5940,19 +5932,19 @@
         <v>18</v>
       </c>
       <c r="AJ32" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="AK32" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM32" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="AK32" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AL32" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM32" t="s" s="2">
+      <c r="AN32" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>18</v>
@@ -5963,10 +5955,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5989,13 +5981,13 @@
         <v>18</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6046,7 +6038,7 @@
         <v>18</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -6070,7 +6062,7 @@
         <v>18</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>18</v>
@@ -6081,10 +6073,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6113,7 +6105,7 @@
         <v>137</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="N34" t="s" s="2">
         <v>139</v>
@@ -6166,7 +6158,7 @@
         <v>18</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -6190,7 +6182,7 @@
         <v>18</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>18</v>
@@ -6201,14 +6193,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6230,10 +6222,10 @@
         <v>136</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="N35" t="s" s="2">
         <v>139</v>
@@ -6288,7 +6280,7 @@
         <v>18</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -6323,10 +6315,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6349,13 +6341,13 @@
         <v>18</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6406,7 +6398,7 @@
         <v>18</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -6415,7 +6407,7 @@
         <v>90</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>102</v>
@@ -6427,10 +6419,10 @@
         <v>18</v>
       </c>
       <c r="AM36" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>18</v>
@@ -6441,10 +6433,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6467,13 +6459,13 @@
         <v>18</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6524,7 +6516,7 @@
         <v>18</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6533,7 +6525,7 @@
         <v>90</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>102</v>
@@ -6545,10 +6537,10 @@
         <v>18</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>18</v>
@@ -6559,10 +6551,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6588,16 +6580,16 @@
         <v>188</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="N38" t="s" s="2">
+      <c r="O38" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>18</v>
@@ -6625,11 +6617,11 @@
         <v>114</v>
       </c>
       <c r="Y38" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="Z38" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="Z38" t="s" s="2">
-        <v>391</v>
-      </c>
       <c r="AA38" t="s" s="2">
         <v>18</v>
       </c>
@@ -6646,7 +6638,7 @@
         <v>18</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6664,13 +6656,13 @@
         <v>18</v>
       </c>
       <c r="AL38" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AM38" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="AM38" t="s" s="2">
-        <v>393</v>
-      </c>
       <c r="AN38" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>18</v>
@@ -6681,10 +6673,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6710,16 +6702,16 @@
         <v>188</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="N39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>398</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>18</v>
@@ -6744,14 +6736,14 @@
         <v>18</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Y39" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="Z39" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="Z39" t="s" s="2">
-        <v>400</v>
-      </c>
       <c r="AA39" t="s" s="2">
         <v>18</v>
       </c>
@@ -6768,7 +6760,7 @@
         <v>18</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6786,13 +6778,13 @@
         <v>18</v>
       </c>
       <c r="AL39" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AM39" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="AM39" t="s" s="2">
-        <v>393</v>
-      </c>
       <c r="AN39" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>18</v>
@@ -6803,10 +6795,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6829,17 +6821,17 @@
         <v>18</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>18</v>
@@ -6888,7 +6880,7 @@
         <v>18</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6912,7 +6904,7 @@
         <v>18</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>18</v>
@@ -6923,10 +6915,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6949,13 +6941,13 @@
         <v>18</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7006,7 +6998,7 @@
         <v>18</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -7027,10 +7019,10 @@
         <v>18</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>18</v>
@@ -7041,10 +7033,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7067,16 +7059,16 @@
         <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7126,7 +7118,7 @@
         <v>18</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -7147,10 +7139,10 @@
         <v>18</v>
       </c>
       <c r="AM42" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AN42" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>18</v>
@@ -7161,10 +7153,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7187,16 +7179,16 @@
         <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7246,7 +7238,7 @@
         <v>18</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -7267,10 +7259,10 @@
         <v>18</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>18</v>
@@ -7281,10 +7273,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7307,19 +7299,19 @@
         <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="N44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>18</v>
@@ -7356,17 +7348,17 @@
         <v>18</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AC44" s="2"/>
       <c r="AD44" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -7387,10 +7379,10 @@
         <v>18</v>
       </c>
       <c r="AM44" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AN44" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>18</v>
@@ -7401,10 +7393,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7427,13 +7419,13 @@
         <v>18</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7484,7 +7476,7 @@
         <v>18</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7508,7 +7500,7 @@
         <v>18</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>18</v>
@@ -7519,10 +7511,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7551,7 +7543,7 @@
         <v>137</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>139</v>
@@ -7604,7 +7596,7 @@
         <v>18</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7628,7 +7620,7 @@
         <v>18</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>18</v>
@@ -7639,14 +7631,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7668,10 +7660,10 @@
         <v>136</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>139</v>
@@ -7726,7 +7718,7 @@
         <v>18</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7761,10 +7753,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7790,16 +7782,16 @@
         <v>188</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="N48" t="s" s="2">
-        <v>438</v>
-      </c>
       <c r="O48" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>18</v>
@@ -7824,14 +7816,14 @@
         <v>18</v>
       </c>
       <c r="X48" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="Y48" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="Y48" t="s" s="2">
+      <c r="Z48" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="Z48" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="AA48" t="s" s="2">
         <v>18</v>
       </c>
@@ -7848,7 +7840,7 @@
         <v>18</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>90</v>
@@ -7866,16 +7858,16 @@
         <v>18</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AM48" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AN48" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AN48" t="s" s="2">
+      <c r="AO48" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AO48" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>18</v>
@@ -7883,10 +7875,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7909,19 +7901,19 @@
         <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="N49" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="M49" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>443</v>
-      </c>
       <c r="O49" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>18</v>
@@ -7970,7 +7962,7 @@
         <v>18</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7988,27 +7980,27 @@
         <v>18</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AM49" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AN49" t="s" s="2">
+      <c r="AO49" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP49" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP49" t="s" s="2">
-        <v>284</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8034,16 +8026,16 @@
         <v>188</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="N50" t="s" s="2">
-        <v>448</v>
-      </c>
       <c r="O50" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>18</v>
@@ -8068,14 +8060,14 @@
         <v>18</v>
       </c>
       <c r="X50" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="Y50" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="Y50" t="s" s="2">
+      <c r="Z50" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="Z50" t="s" s="2">
-        <v>292</v>
-      </c>
       <c r="AA50" t="s" s="2">
         <v>18</v>
       </c>
@@ -8092,7 +8084,7 @@
         <v>18</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -8101,7 +8093,7 @@
         <v>90</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>102</v>
@@ -8116,7 +8108,7 @@
         <v>133</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>18</v>
@@ -8127,14 +8119,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8156,16 +8148,16 @@
         <v>188</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="N51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>18</v>
@@ -8190,14 +8182,14 @@
         <v>18</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Y51" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="Z51" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="Z51" t="s" s="2">
-        <v>302</v>
-      </c>
       <c r="AA51" t="s" s="2">
         <v>18</v>
       </c>
@@ -8214,7 +8206,7 @@
         <v>18</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -8232,27 +8224,27 @@
         <v>18</v>
       </c>
       <c r="AL51" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AM51" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="AM51" t="s" s="2">
+      <c r="AN51" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="AN51" t="s" s="2">
+      <c r="AO51" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP51" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP51" t="s" s="2">
-        <v>306</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8278,16 +8270,16 @@
         <v>80</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="M52" t="s" s="2">
-        <v>452</v>
-      </c>
       <c r="N52" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="O52" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>18</v>
@@ -8336,7 +8328,7 @@
         <v>18</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -8357,10 +8349,10 @@
         <v>18</v>
       </c>
       <c r="AM52" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AN52" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>18</v>
@@ -8371,13 +8363,13 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="C53" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="C53" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="D53" t="s" s="2">
         <v>18</v>
@@ -8399,19 +8391,19 @@
         <v>91</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="N53" t="s" s="2">
+      <c r="O53" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>18</v>
@@ -8460,7 +8452,7 @@
         <v>18</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8481,10 +8473,10 @@
         <v>18</v>
       </c>
       <c r="AM53" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AN53" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>18</v>
@@ -8495,10 +8487,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8521,13 +8513,13 @@
         <v>18</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8578,7 +8570,7 @@
         <v>18</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8602,7 +8594,7 @@
         <v>18</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>18</v>
@@ -8613,10 +8605,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8645,7 +8637,7 @@
         <v>137</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>139</v>
@@ -8698,7 +8690,7 @@
         <v>18</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8722,7 +8714,7 @@
         <v>18</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>18</v>
@@ -8733,14 +8725,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8762,10 +8754,10 @@
         <v>136</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="N56" t="s" s="2">
         <v>139</v>
@@ -8820,7 +8812,7 @@
         <v>18</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8855,10 +8847,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8884,16 +8876,16 @@
         <v>188</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="N57" t="s" s="2">
-        <v>438</v>
-      </c>
       <c r="O57" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>18</v>
@@ -8903,7 +8895,7 @@
         <v>18</v>
       </c>
       <c r="S57" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="T57" t="s" s="2">
         <v>18</v>
@@ -8918,14 +8910,14 @@
         <v>18</v>
       </c>
       <c r="X57" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="Y57" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="Y57" t="s" s="2">
+      <c r="Z57" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="Z57" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="AA57" t="s" s="2">
         <v>18</v>
       </c>
@@ -8942,7 +8934,7 @@
         <v>18</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>90</v>
@@ -8960,16 +8952,16 @@
         <v>18</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AM57" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AN57" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AN57" t="s" s="2">
+      <c r="AO57" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>18</v>
@@ -8977,10 +8969,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9003,19 +8995,19 @@
         <v>91</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>18</v>
@@ -9064,7 +9056,7 @@
         <v>18</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -9082,27 +9074,27 @@
         <v>18</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AM58" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AN58" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AN58" t="s" s="2">
+      <c r="AO58" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP58" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP58" t="s" s="2">
-        <v>284</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9128,16 +9120,16 @@
         <v>188</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="N59" t="s" s="2">
-        <v>448</v>
-      </c>
       <c r="O59" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>18</v>
@@ -9162,14 +9154,14 @@
         <v>18</v>
       </c>
       <c r="X59" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="Y59" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="Y59" t="s" s="2">
+      <c r="Z59" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="Z59" t="s" s="2">
-        <v>292</v>
-      </c>
       <c r="AA59" t="s" s="2">
         <v>18</v>
       </c>
@@ -9186,7 +9178,7 @@
         <v>18</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -9195,7 +9187,7 @@
         <v>90</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>102</v>
@@ -9210,7 +9202,7 @@
         <v>133</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>18</v>
@@ -9221,14 +9213,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9250,16 +9242,16 @@
         <v>188</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="M60" t="s" s="2">
+      <c r="N60" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="N60" t="s" s="2">
+      <c r="O60" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>18</v>
@@ -9284,14 +9276,14 @@
         <v>18</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Y60" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="Z60" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="Z60" t="s" s="2">
-        <v>302</v>
-      </c>
       <c r="AA60" t="s" s="2">
         <v>18</v>
       </c>
@@ -9308,7 +9300,7 @@
         <v>18</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -9326,27 +9318,27 @@
         <v>18</v>
       </c>
       <c r="AL60" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AM60" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="AM60" t="s" s="2">
+      <c r="AN60" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="AN60" t="s" s="2">
+      <c r="AO60" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP60" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP60" t="s" s="2">
-        <v>306</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9372,16 +9364,16 @@
         <v>80</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="M61" t="s" s="2">
-        <v>452</v>
-      </c>
       <c r="N61" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="O61" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>18</v>
@@ -9430,7 +9422,7 @@
         <v>18</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -9451,10 +9443,10 @@
         <v>18</v>
       </c>
       <c r="AM61" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AN61" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>18</v>
@@ -9465,13 +9457,13 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="C62" t="s" s="2">
         <v>465</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="C62" t="s" s="2">
-        <v>466</v>
       </c>
       <c r="D62" t="s" s="2">
         <v>18</v>
@@ -9493,19 +9485,19 @@
         <v>91</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="N62" t="s" s="2">
+      <c r="O62" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>18</v>
@@ -9554,7 +9546,7 @@
         <v>18</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9575,10 +9567,10 @@
         <v>18</v>
       </c>
       <c r="AM62" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AN62" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>18</v>
@@ -9589,10 +9581,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9615,13 +9607,13 @@
         <v>18</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9672,7 +9664,7 @@
         <v>18</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9696,7 +9688,7 @@
         <v>18</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>18</v>
@@ -9707,10 +9699,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9739,7 +9731,7 @@
         <v>137</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="N64" t="s" s="2">
         <v>139</v>
@@ -9792,7 +9784,7 @@
         <v>18</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9816,7 +9808,7 @@
         <v>18</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>18</v>
@@ -9827,14 +9819,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -9856,10 +9848,10 @@
         <v>136</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="N65" t="s" s="2">
         <v>139</v>
@@ -9914,7 +9906,7 @@
         <v>18</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -9949,10 +9941,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9978,16 +9970,16 @@
         <v>188</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="N66" t="s" s="2">
-        <v>438</v>
-      </c>
       <c r="O66" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>18</v>
@@ -9997,7 +9989,7 @@
         <v>18</v>
       </c>
       <c r="S66" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="T66" t="s" s="2">
         <v>18</v>
@@ -10012,14 +10004,14 @@
         <v>18</v>
       </c>
       <c r="X66" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="Y66" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="Y66" t="s" s="2">
+      <c r="Z66" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="Z66" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="AA66" t="s" s="2">
         <v>18</v>
       </c>
@@ -10036,7 +10028,7 @@
         <v>18</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>90</v>
@@ -10054,16 +10046,16 @@
         <v>18</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AM66" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AN66" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AN66" t="s" s="2">
+      <c r="AO66" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AO66" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>18</v>
@@ -10071,10 +10063,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10097,19 +10089,19 @@
         <v>91</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="N67" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="M67" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>443</v>
-      </c>
       <c r="O67" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>18</v>
@@ -10158,7 +10150,7 @@
         <v>18</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -10176,27 +10168,27 @@
         <v>18</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AM67" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AN67" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AN67" t="s" s="2">
+      <c r="AO67" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP67" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="AO67" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP67" t="s" s="2">
-        <v>284</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="B68" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>475</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10219,13 +10211,13 @@
         <v>18</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10276,7 +10268,7 @@
         <v>18</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -10300,7 +10292,7 @@
         <v>18</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>18</v>
@@ -10311,10 +10303,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="B69" t="s" s="2">
         <v>476</v>
-      </c>
-      <c r="B69" t="s" s="2">
-        <v>477</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10343,7 +10335,7 @@
         <v>137</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="N69" t="s" s="2">
         <v>139</v>
@@ -10384,19 +10376,19 @@
         <v>18</v>
       </c>
       <c r="AB69" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="AC69" t="s" s="2">
         <v>478</v>
       </c>
-      <c r="AC69" t="s" s="2">
-        <v>479</v>
-      </c>
       <c r="AD69" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10420,7 +10412,7 @@
         <v>18</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>18</v>
@@ -10431,10 +10423,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="B70" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="B70" t="s" s="2">
-        <v>481</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10457,19 +10449,19 @@
         <v>91</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="L70" t="s" s="2">
         <v>482</v>
       </c>
-      <c r="L70" t="s" s="2">
+      <c r="M70" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="N70" t="s" s="2">
+      <c r="O70" t="s" s="2">
         <v>485</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>486</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>18</v>
@@ -10518,7 +10510,7 @@
         <v>18</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10539,10 +10531,10 @@
         <v>18</v>
       </c>
       <c r="AM70" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AN70" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>489</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>18</v>
@@ -10553,10 +10545,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="B71" t="s" s="2">
         <v>490</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>491</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10582,20 +10574,20 @@
         <v>110</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>492</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>493</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="P71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Q71" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="P71" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Q71" t="s" s="2">
-        <v>495</v>
       </c>
       <c r="R71" t="s" s="2">
         <v>18</v>
@@ -10619,28 +10611,28 @@
         <v>179</v>
       </c>
       <c r="Y71" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="Z71" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="Z71" t="s" s="2">
+      <c r="AA71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF71" t="s" s="2">
         <v>497</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -10661,10 +10653,10 @@
         <v>18</v>
       </c>
       <c r="AM71" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="AN71" t="s" s="2">
         <v>499</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>500</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>18</v>
@@ -10675,10 +10667,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="B72" t="s" s="2">
         <v>501</v>
-      </c>
-      <c r="B72" t="s" s="2">
-        <v>502</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10701,17 +10693,17 @@
         <v>91</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>504</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>18</v>
@@ -10721,46 +10713,46 @@
         <v>18</v>
       </c>
       <c r="S72" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF72" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="T72" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="U72" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="V72" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="W72" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="X72" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Y72" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Z72" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF72" t="s" s="2">
-        <v>507</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10781,10 +10773,10 @@
         <v>18</v>
       </c>
       <c r="AM72" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="AN72" t="s" s="2">
         <v>508</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>509</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>18</v>
@@ -10795,10 +10787,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="B73" t="s" s="2">
         <v>510</v>
-      </c>
-      <c r="B73" t="s" s="2">
-        <v>511</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10824,14 +10816,14 @@
         <v>104</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>512</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>513</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>18</v>
@@ -10841,46 +10833,46 @@
         <v>18</v>
       </c>
       <c r="S73" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF73" t="s" s="2">
         <v>515</v>
-      </c>
-      <c r="T73" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="U73" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="V73" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="W73" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="X73" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Y73" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Z73" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AA73" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB73" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC73" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD73" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE73" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF73" t="s" s="2">
-        <v>516</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10889,7 +10881,7 @@
         <v>90</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>102</v>
@@ -10901,10 +10893,10 @@
         <v>18</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>18</v>
@@ -10915,10 +10907,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="B74" t="s" s="2">
         <v>519</v>
-      </c>
-      <c r="B74" t="s" s="2">
-        <v>520</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10944,16 +10936,16 @@
         <v>110</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="N74" t="s" s="2">
+      <c r="O74" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>18</v>
@@ -10963,7 +10955,7 @@
         <v>18</v>
       </c>
       <c r="S74" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="T74" t="s" s="2">
         <v>18</v>
@@ -11002,7 +10994,7 @@
         <v>18</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -11023,10 +11015,10 @@
         <v>18</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>18</v>
@@ -11037,10 +11029,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11066,16 +11058,16 @@
         <v>188</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="N75" t="s" s="2">
-        <v>448</v>
-      </c>
       <c r="O75" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>18</v>
@@ -11100,14 +11092,14 @@
         <v>18</v>
       </c>
       <c r="X75" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="Y75" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="Y75" t="s" s="2">
+      <c r="Z75" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="Z75" t="s" s="2">
-        <v>292</v>
-      </c>
       <c r="AA75" t="s" s="2">
         <v>18</v>
       </c>
@@ -11124,7 +11116,7 @@
         <v>18</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -11133,7 +11125,7 @@
         <v>90</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>102</v>
@@ -11148,7 +11140,7 @@
         <v>133</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>18</v>
@@ -11159,14 +11151,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -11188,16 +11180,16 @@
         <v>188</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="N76" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="N76" t="s" s="2">
+      <c r="O76" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>18</v>
@@ -11222,14 +11214,14 @@
         <v>18</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Y76" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="Z76" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="Z76" t="s" s="2">
-        <v>302</v>
-      </c>
       <c r="AA76" t="s" s="2">
         <v>18</v>
       </c>
@@ -11246,7 +11238,7 @@
         <v>18</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -11264,27 +11256,27 @@
         <v>18</v>
       </c>
       <c r="AL76" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AM76" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="AM76" t="s" s="2">
+      <c r="AN76" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="AN76" t="s" s="2">
+      <c r="AO76" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP76" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="AO76" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP76" t="s" s="2">
-        <v>306</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11310,16 +11302,16 @@
         <v>80</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="M77" t="s" s="2">
-        <v>452</v>
-      </c>
       <c r="N77" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="O77" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>18</v>
@@ -11368,7 +11360,7 @@
         <v>18</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -11389,10 +11381,10 @@
         <v>18</v>
       </c>
       <c r="AM77" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AN77" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="AN77" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>18</v>
@@ -11403,13 +11395,13 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="C78" t="s" s="2">
         <v>530</v>
-      </c>
-      <c r="B78" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="C78" t="s" s="2">
-        <v>531</v>
       </c>
       <c r="D78" t="s" s="2">
         <v>18</v>
@@ -11431,19 +11423,19 @@
         <v>91</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="M78" t="s" s="2">
+      <c r="N78" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="N78" t="s" s="2">
+      <c r="O78" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>18</v>
@@ -11492,7 +11484,7 @@
         <v>18</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -11513,10 +11505,10 @@
         <v>18</v>
       </c>
       <c r="AM78" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AN78" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>18</v>
@@ -11527,10 +11519,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11553,13 +11545,13 @@
         <v>18</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M79" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11610,7 +11602,7 @@
         <v>18</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -11634,7 +11626,7 @@
         <v>18</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>18</v>
@@ -11645,10 +11637,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11677,7 +11669,7 @@
         <v>137</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="N80" t="s" s="2">
         <v>139</v>
@@ -11730,7 +11722,7 @@
         <v>18</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -11754,7 +11746,7 @@
         <v>18</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>18</v>
@@ -11765,14 +11757,14 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -11794,10 +11786,10 @@
         <v>136</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="N81" t="s" s="2">
         <v>139</v>
@@ -11852,7 +11844,7 @@
         <v>18</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -11887,10 +11879,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11916,16 +11908,16 @@
         <v>188</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="M82" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="M82" t="s" s="2">
+      <c r="N82" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="N82" t="s" s="2">
-        <v>438</v>
-      </c>
       <c r="O82" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>18</v>
@@ -11935,7 +11927,7 @@
         <v>18</v>
       </c>
       <c r="S82" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="T82" t="s" s="2">
         <v>18</v>
@@ -11950,14 +11942,14 @@
         <v>18</v>
       </c>
       <c r="X82" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="Y82" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="Y82" t="s" s="2">
+      <c r="Z82" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="Z82" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="AA82" t="s" s="2">
         <v>18</v>
       </c>
@@ -11974,7 +11966,7 @@
         <v>18</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>90</v>
@@ -11992,16 +11984,16 @@
         <v>18</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AM82" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AN82" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AN82" t="s" s="2">
+      <c r="AO82" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AO82" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="AP82" t="s" s="2">
         <v>18</v>
@@ -12009,10 +12001,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12035,19 +12027,19 @@
         <v>91</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="N83" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="M83" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>443</v>
-      </c>
       <c r="O83" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>18</v>
@@ -12096,7 +12088,7 @@
         <v>18</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -12114,27 +12106,27 @@
         <v>18</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AM83" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AN83" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AN83" t="s" s="2">
+      <c r="AO83" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP83" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="AO83" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP83" t="s" s="2">
-        <v>284</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12160,16 +12152,16 @@
         <v>188</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="N84" t="s" s="2">
-        <v>448</v>
-      </c>
       <c r="O84" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>18</v>
@@ -12194,14 +12186,14 @@
         <v>18</v>
       </c>
       <c r="X84" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="Y84" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="Y84" t="s" s="2">
+      <c r="Z84" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="Z84" t="s" s="2">
-        <v>292</v>
-      </c>
       <c r="AA84" t="s" s="2">
         <v>18</v>
       </c>
@@ -12218,7 +12210,7 @@
         <v>18</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -12227,7 +12219,7 @@
         <v>90</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AJ84" t="s" s="2">
         <v>102</v>
@@ -12242,7 +12234,7 @@
         <v>133</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>18</v>
@@ -12253,14 +12245,14 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -12282,16 +12274,16 @@
         <v>188</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="M85" t="s" s="2">
+      <c r="N85" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="N85" t="s" s="2">
+      <c r="O85" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>18</v>
@@ -12316,14 +12308,14 @@
         <v>18</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Y85" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="Z85" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="Z85" t="s" s="2">
-        <v>302</v>
-      </c>
       <c r="AA85" t="s" s="2">
         <v>18</v>
       </c>
@@ -12340,7 +12332,7 @@
         <v>18</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -12358,27 +12350,27 @@
         <v>18</v>
       </c>
       <c r="AL85" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AM85" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="AM85" t="s" s="2">
+      <c r="AN85" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="AN85" t="s" s="2">
+      <c r="AO85" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP85" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="AO85" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP85" t="s" s="2">
-        <v>306</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12404,16 +12396,16 @@
         <v>80</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="M86" t="s" s="2">
-        <v>452</v>
-      </c>
       <c r="N86" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="O86" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>18</v>
@@ -12462,7 +12454,7 @@
         <v>18</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -12483,10 +12475,10 @@
         <v>18</v>
       </c>
       <c r="AM86" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AN86" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="AN86" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>18</v>

--- a/StructureDefinition-onc-sleep-pattern.xlsx
+++ b/StructureDefinition-onc-sleep-pattern.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T09:46:48+00:00</t>
+    <t>2026-07-11T14:02:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-sleep-pattern.xlsx
+++ b/StructureDefinition-onc-sleep-pattern.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T14:02:42+00:00</t>
+    <t>2026-07-11T14:17:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-sleep-pattern.xlsx
+++ b/StructureDefinition-onc-sleep-pattern.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T14:17:07+00:00</t>
+    <t>2026-07-11T14:32:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-sleep-pattern.xlsx
+++ b/StructureDefinition-onc-sleep-pattern.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T14:32:04+00:00</t>
+    <t>2026-07-11T14:47:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-sleep-pattern.xlsx
+++ b/StructureDefinition-onc-sleep-pattern.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T14:47:20+00:00</t>
+    <t>2026-07-11T18:02:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
